--- a/NIFTY_200_Technical_Metrics.xlsx
+++ b/NIFTY_200_Technical_Metrics.xlsx
@@ -2607,7 +2607,7 @@
         <v>57</v>
       </c>
       <c r="P2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q2">
         <v>1054.32</v>
@@ -2723,7 +2723,7 @@
         <v>87</v>
       </c>
       <c r="P3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q3">
         <v>6914.5</v>
@@ -2839,7 +2839,7 @@
         <v>84</v>
       </c>
       <c r="P4">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>375.55</v>
@@ -2955,7 +2955,7 @@
         <v>78</v>
       </c>
       <c r="P5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q5">
         <v>1307.16</v>
@@ -3071,7 +3071,7 @@
         <v>44</v>
       </c>
       <c r="P6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q6">
         <v>2737.46</v>
@@ -3187,7 +3187,7 @@
         <v>69</v>
       </c>
       <c r="P7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q7">
         <v>1285.98</v>
@@ -3303,7 +3303,7 @@
         <v>86</v>
       </c>
       <c r="P8">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q8">
         <v>1755.3</v>
@@ -3419,7 +3419,7 @@
         <v>76</v>
       </c>
       <c r="P9">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>195.47</v>
@@ -3651,7 +3651,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q11">
         <v>355.49</v>
@@ -3767,7 +3767,7 @@
         <v>92</v>
       </c>
       <c r="P12">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q12">
         <v>2108.18</v>
@@ -3883,7 +3883,7 @@
         <v>60</v>
       </c>
       <c r="P13">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q13">
         <v>7902</v>
@@ -3999,7 +3999,7 @@
         <v>62</v>
       </c>
       <c r="P14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q14">
         <v>149.12</v>
@@ -4115,7 +4115,7 @@
         <v>48</v>
       </c>
       <c r="P15">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q15">
         <v>2362.6</v>
@@ -4231,7 +4231,7 @@
         <v>74</v>
       </c>
       <c r="P16">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q16">
         <v>1402.08</v>
@@ -4347,7 +4347,7 @@
         <v>24</v>
       </c>
       <c r="P17">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q17">
         <v>575.85</v>
@@ -4463,7 +4463,7 @@
         <v>83</v>
       </c>
       <c r="P18">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q18">
         <v>1001.52</v>
@@ -4579,7 +4579,7 @@
         <v>96</v>
       </c>
       <c r="P19">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q19">
         <v>1677.54</v>
@@ -4695,7 +4695,7 @@
         <v>70</v>
       </c>
       <c r="P20">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q20">
         <v>1243.36</v>
@@ -4927,7 +4927,7 @@
         <v>32</v>
       </c>
       <c r="P22">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q22">
         <v>1737.96</v>
@@ -5043,7 +5043,7 @@
         <v>61</v>
       </c>
       <c r="P23">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q23">
         <v>10682.8</v>
@@ -5159,7 +5159,7 @@
         <v>49</v>
       </c>
       <c r="P24">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q24">
         <v>962.58</v>
@@ -5275,7 +5275,7 @@
         <v>49</v>
       </c>
       <c r="P25">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q25">
         <v>233.98</v>
@@ -5391,7 +5391,7 @@
         <v>71</v>
       </c>
       <c r="P26">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q26">
         <v>133.2</v>
@@ -5507,7 +5507,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q27">
         <v>1081.88</v>
@@ -5623,7 +5623,7 @@
         <v>34</v>
       </c>
       <c r="P28">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q28">
         <v>377.2</v>
@@ -5739,7 +5739,7 @@
         <v>90</v>
       </c>
       <c r="P29">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q29">
         <v>1832.46</v>
@@ -5971,7 +5971,7 @@
         <v>97</v>
       </c>
       <c r="P31">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q31">
         <v>438.54</v>
@@ -6087,7 +6087,7 @@
         <v>43</v>
       </c>
       <c r="P32">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q32">
         <v>359.66</v>
@@ -6203,7 +6203,7 @@
         <v>46</v>
       </c>
       <c r="P33">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q33">
         <v>1540.92</v>
@@ -6319,7 +6319,7 @@
         <v>81</v>
       </c>
       <c r="P34">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q34">
         <v>44214</v>
@@ -6435,7 +6435,7 @@
         <v>42</v>
       </c>
       <c r="P35">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q35">
         <v>293.57</v>
@@ -6551,7 +6551,7 @@
         <v>30</v>
       </c>
       <c r="P36">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q36">
         <v>4800.88</v>
@@ -6667,7 +6667,7 @@
         <v>91</v>
       </c>
       <c r="P37">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q37">
         <v>3292.52</v>
@@ -6783,7 +6783,7 @@
         <v>55</v>
       </c>
       <c r="P38">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q38">
         <v>118.48</v>
@@ -6899,7 +6899,7 @@
         <v>74</v>
       </c>
       <c r="P39">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q39">
         <v>881.28</v>
@@ -7015,7 +7015,7 @@
         <v>43</v>
       </c>
       <c r="P40">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q40">
         <v>1582.54</v>
@@ -7131,7 +7131,7 @@
         <v>36</v>
       </c>
       <c r="P41">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q41">
         <v>1322.14</v>
@@ -7247,7 +7247,7 @@
         <v>77</v>
       </c>
       <c r="P42">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q42">
         <v>414.43</v>
@@ -7363,7 +7363,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q43">
         <v>1250.18</v>
@@ -7479,7 +7479,7 @@
         <v>92</v>
       </c>
       <c r="P44">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q44">
         <v>1841.22</v>
@@ -7595,7 +7595,7 @@
         <v>33</v>
       </c>
       <c r="P45">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q45">
         <v>1779.06</v>
@@ -7711,7 +7711,7 @@
         <v>35</v>
       </c>
       <c r="P46">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q46">
         <v>440.61</v>
@@ -7827,7 +7827,7 @@
         <v>13</v>
       </c>
       <c r="P47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q47">
         <v>1742.46</v>
@@ -7943,7 +7943,7 @@
         <v>77</v>
       </c>
       <c r="P48">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q48">
         <v>4838.88</v>
@@ -8059,7 +8059,7 @@
         <v>30</v>
       </c>
       <c r="P49">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q49">
         <v>382.92</v>
@@ -8407,7 +8407,7 @@
         <v>44</v>
       </c>
       <c r="P52">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q52">
         <v>656.13</v>
@@ -8523,7 +8523,7 @@
         <v>28</v>
       </c>
       <c r="P53">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q53">
         <v>3577.34</v>
@@ -8639,7 +8639,7 @@
         <v>63</v>
       </c>
       <c r="P54">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q54">
         <v>1198.36</v>
@@ -8755,7 +8755,7 @@
         <v>62</v>
       </c>
       <c r="P55">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q55">
         <v>6970</v>
@@ -8871,7 +8871,7 @@
         <v>46</v>
       </c>
       <c r="P56">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Q56">
         <v>3249.78</v>
@@ -8987,7 +8987,7 @@
         <v>79</v>
       </c>
       <c r="P57">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q57">
         <v>324.06</v>
@@ -9219,7 +9219,7 @@
         <v>97</v>
       </c>
       <c r="P59">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q59">
         <v>324.37</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="P60">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q60">
         <v>771.23</v>
@@ -9451,7 +9451,7 @@
         <v>58</v>
       </c>
       <c r="P61">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q61">
         <v>168.93</v>
@@ -9567,7 +9567,7 @@
         <v>82</v>
       </c>
       <c r="P62">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q62">
         <v>2274.7</v>
@@ -9683,7 +9683,7 @@
         <v>47</v>
       </c>
       <c r="P63">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q63">
         <v>91.42</v>
@@ -9799,7 +9799,7 @@
         <v>4</v>
       </c>
       <c r="P64">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q64">
         <v>1844.52</v>
@@ -9915,7 +9915,7 @@
         <v>18</v>
       </c>
       <c r="P65">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q65">
         <v>860.11</v>
@@ -10031,7 +10031,7 @@
         <v>7</v>
       </c>
       <c r="P66">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q66">
         <v>1574.82</v>
@@ -10147,7 +10147,7 @@
         <v>52</v>
       </c>
       <c r="P67">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q67">
         <v>2921.78</v>
@@ -10370,7 +10370,7 @@
         <v>85</v>
       </c>
       <c r="P69">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q69">
         <v>4240.66</v>
@@ -10602,7 +10602,7 @@
         <v>17</v>
       </c>
       <c r="P71">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q71">
         <v>1045.88</v>
@@ -10718,7 +10718,7 @@
         <v>59</v>
       </c>
       <c r="P72">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q72">
         <v>1196.98</v>
@@ -10834,7 +10834,7 @@
         <v>23</v>
       </c>
       <c r="P73">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q73">
         <v>2304.14</v>
@@ -10950,7 +10950,7 @@
         <v>21</v>
       </c>
       <c r="P74">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q74">
         <v>703.7</v>
@@ -11066,7 +11066,7 @@
         <v>35</v>
       </c>
       <c r="P75">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q75">
         <v>544.4299999999999</v>
@@ -11182,7 +11182,7 @@
         <v>48</v>
       </c>
       <c r="P76">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q76">
         <v>4984.1</v>
@@ -11298,7 +11298,7 @@
         <v>73</v>
       </c>
       <c r="P77">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q77">
         <v>916.05</v>
@@ -11414,7 +11414,7 @@
         <v>16</v>
       </c>
       <c r="P78">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q78">
         <v>337.82</v>
@@ -11646,7 +11646,7 @@
         <v>81</v>
       </c>
       <c r="P80">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q80">
         <v>548.97</v>
@@ -11762,7 +11762,7 @@
         <v>9</v>
       </c>
       <c r="P81">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q81">
         <v>160.33</v>
@@ -12217,7 +12217,7 @@
         <v>54</v>
       </c>
       <c r="P85">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Q85">
         <v>1620.5</v>
@@ -12333,7 +12333,7 @@
         <v>93</v>
       </c>
       <c r="P86">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q86">
         <v>12.99</v>
@@ -12449,7 +12449,7 @@
         <v>76</v>
       </c>
       <c r="P87">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q87">
         <v>80.26000000000001</v>
@@ -12565,7 +12565,7 @@
         <v>63</v>
       </c>
       <c r="P88">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q88">
         <v>723.92</v>
@@ -12681,7 +12681,7 @@
         <v>75</v>
       </c>
       <c r="P89">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q89">
         <v>817.78</v>
@@ -12797,7 +12797,7 @@
         <v>37</v>
       </c>
       <c r="P90">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q90">
         <v>4924.32</v>
@@ -13029,7 +13029,7 @@
         <v>72</v>
       </c>
       <c r="P92">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q92">
         <v>381.64</v>
@@ -13145,7 +13145,7 @@
         <v>27</v>
       </c>
       <c r="P93">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q93">
         <v>1009.35</v>
@@ -13261,7 +13261,7 @@
         <v>34</v>
       </c>
       <c r="P94">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q94">
         <v>128.94</v>
@@ -13377,7 +13377,7 @@
         <v>19</v>
       </c>
       <c r="P95">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q95">
         <v>453.98</v>
@@ -13493,7 +13493,7 @@
         <v>13</v>
       </c>
       <c r="P96">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q96">
         <v>106.71</v>
@@ -13609,7 +13609,7 @@
         <v>8</v>
       </c>
       <c r="P97">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q97">
         <v>75.75</v>
@@ -13725,7 +13725,7 @@
         <v>26</v>
       </c>
       <c r="P98">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q98">
         <v>264.46</v>
@@ -13841,7 +13841,7 @@
         <v>53</v>
       </c>
       <c r="P99">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q99">
         <v>1054.18</v>
@@ -13957,7 +13957,7 @@
         <v>18</v>
       </c>
       <c r="P100">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q100">
         <v>214.39</v>
@@ -14073,7 +14073,7 @@
         <v>24</v>
       </c>
       <c r="P101">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q101">
         <v>480.26</v>
@@ -14189,7 +14189,7 @@
         <v>56</v>
       </c>
       <c r="P102">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q102">
         <v>1213.62</v>
@@ -14305,7 +14305,7 @@
         <v>21</v>
       </c>
       <c r="P103">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q103">
         <v>441.28</v>
@@ -14421,7 +14421,7 @@
         <v>88</v>
       </c>
       <c r="P104">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="Q104">
         <v>556.3</v>
@@ -14537,7 +14537,7 @@
         <v>69</v>
       </c>
       <c r="P105">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q105">
         <v>4607.66</v>
@@ -14653,7 +14653,7 @@
         <v>86</v>
       </c>
       <c r="P106">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q106">
         <v>432.78</v>
@@ -15215,7 +15215,7 @@
         <v>65</v>
       </c>
       <c r="P111">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Q111">
         <v>522.21</v>
@@ -15331,7 +15331,7 @@
         <v>41</v>
       </c>
       <c r="P112">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q112">
         <v>1101.58</v>
@@ -15447,7 +15447,7 @@
         <v>58</v>
       </c>
       <c r="P113">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q113">
         <v>3709.98</v>
@@ -15563,7 +15563,7 @@
         <v>38</v>
       </c>
       <c r="P114">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q114">
         <v>261.4</v>
@@ -15679,7 +15679,7 @@
         <v>39</v>
       </c>
       <c r="P115">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q115">
         <v>3979.22</v>
@@ -15795,7 +15795,7 @@
         <v>40</v>
       </c>
       <c r="P116">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q116">
         <v>1989.32</v>
@@ -16027,7 +16027,7 @@
         <v>68</v>
       </c>
       <c r="P118">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Q118">
         <v>321.13</v>
@@ -16143,7 +16143,7 @@
         <v>60</v>
       </c>
       <c r="P119">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q119">
         <v>2445.5</v>
@@ -16259,7 +16259,7 @@
         <v>70</v>
       </c>
       <c r="P120">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q120">
         <v>786.96</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="P121">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q121">
         <v>11451</v>
@@ -16491,7 +16491,7 @@
         <v>16</v>
       </c>
       <c r="P122">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q122">
         <v>896.9400000000001</v>
@@ -16839,7 +16839,7 @@
         <v>19</v>
       </c>
       <c r="P125">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q125">
         <v>1337.24</v>
@@ -16955,7 +16955,7 @@
         <v>94</v>
       </c>
       <c r="P126">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q126">
         <v>156.36</v>
@@ -17187,7 +17187,7 @@
         <v>51</v>
       </c>
       <c r="P128">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q128">
         <v>2309.5</v>
@@ -17303,7 +17303,7 @@
         <v>31</v>
       </c>
       <c r="P129">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q129">
         <v>123008</v>
@@ -17419,7 +17419,7 @@
         <v>23</v>
       </c>
       <c r="P130">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q130">
         <v>2648.22</v>
@@ -17651,7 +17651,7 @@
         <v>52</v>
       </c>
       <c r="P132">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q132">
         <v>1213.96</v>
@@ -17883,7 +17883,7 @@
         <v>39</v>
       </c>
       <c r="P134">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q134">
         <v>72.45</v>
@@ -17999,7 +17999,7 @@
         <v>37</v>
       </c>
       <c r="P135">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q135">
         <v>72.68000000000001</v>
@@ -18115,7 +18115,7 @@
         <v>45</v>
       </c>
       <c r="P136">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q136">
         <v>316.34</v>
@@ -18231,7 +18231,7 @@
         <v>93</v>
       </c>
       <c r="P137">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q137">
         <v>338.86</v>
@@ -18347,7 +18347,7 @@
         <v>57</v>
       </c>
       <c r="P138">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q138">
         <v>1720.22</v>
@@ -18463,7 +18463,7 @@
         <v>75</v>
       </c>
       <c r="P139">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q139">
         <v>10487.6</v>
@@ -18579,7 +18579,7 @@
         <v>78</v>
       </c>
       <c r="P140">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q140">
         <v>447.72</v>
@@ -18695,7 +18695,7 @@
         <v>45</v>
       </c>
       <c r="P141">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q141">
         <v>222.41</v>
@@ -18811,7 +18811,7 @@
         <v>47</v>
       </c>
       <c r="P142">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q142">
         <v>37266</v>
@@ -18927,7 +18927,7 @@
         <v>15</v>
       </c>
       <c r="P143">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q143">
         <v>359.02</v>
@@ -19043,7 +19043,7 @@
         <v>95</v>
       </c>
       <c r="P144">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q144">
         <v>1677.5</v>
@@ -19159,7 +19159,7 @@
         <v>89</v>
       </c>
       <c r="P145">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q145">
         <v>5559.2</v>
@@ -19391,7 +19391,7 @@
         <v>66</v>
       </c>
       <c r="P147">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q147">
         <v>1849.66</v>
@@ -19507,7 +19507,7 @@
         <v>56</v>
       </c>
       <c r="P148">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q148">
         <v>1487.76</v>
@@ -19623,7 +19623,7 @@
         <v>5</v>
       </c>
       <c r="P149">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q149">
         <v>2179.64</v>
@@ -19739,7 +19739,7 @@
         <v>84</v>
       </c>
       <c r="P150">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q150">
         <v>114.23</v>
@@ -20087,7 +20087,7 @@
         <v>36</v>
       </c>
       <c r="P153">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q153">
         <v>252.21</v>
@@ -20203,7 +20203,7 @@
         <v>95</v>
       </c>
       <c r="P154">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q154">
         <v>31258</v>
@@ -20319,7 +20319,7 @@
         <v>25</v>
       </c>
       <c r="P155">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q155">
         <v>897.79</v>
@@ -20435,7 +20435,7 @@
         <v>29</v>
       </c>
       <c r="P156">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q156">
         <v>1431.96</v>
@@ -20551,7 +20551,7 @@
         <v>96</v>
       </c>
       <c r="P157">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q157">
         <v>4441.84</v>
@@ -20667,7 +20667,7 @@
         <v>27</v>
       </c>
       <c r="P158">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q158">
         <v>297.91</v>
@@ -20783,7 +20783,7 @@
         <v>32</v>
       </c>
       <c r="P159">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q159">
         <v>1192.08</v>
@@ -20899,7 +20899,7 @@
         <v>4</v>
       </c>
       <c r="P160">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q160">
         <v>193.89</v>
@@ -21015,7 +21015,7 @@
         <v>89</v>
       </c>
       <c r="P161">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Q161">
         <v>173.43</v>
@@ -21247,7 +21247,7 @@
         <v>50</v>
       </c>
       <c r="P163">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q163">
         <v>1710.54</v>
@@ -21363,7 +21363,7 @@
         <v>72</v>
       </c>
       <c r="P164">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q164">
         <v>953.97</v>
@@ -21479,7 +21479,7 @@
         <v>20</v>
       </c>
       <c r="P165">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q165">
         <v>21932</v>
@@ -21595,7 +21595,7 @@
         <v>88</v>
       </c>
       <c r="P166">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q166">
         <v>948.4299999999999</v>
@@ -21711,7 +21711,7 @@
         <v>80</v>
       </c>
       <c r="P167">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q167">
         <v>3716.42</v>
@@ -21827,7 +21827,7 @@
         <v>94</v>
       </c>
       <c r="P168">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q168">
         <v>19906.2</v>
@@ -21943,7 +21943,7 @@
         <v>40</v>
       </c>
       <c r="P169">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q169">
         <v>2478.94</v>
@@ -22175,7 +22175,7 @@
         <v>53</v>
       </c>
       <c r="P171">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q171">
         <v>3476.72</v>
@@ -22291,7 +22291,7 @@
         <v>3</v>
       </c>
       <c r="P172">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q172">
         <v>38.09</v>
@@ -22407,7 +22407,7 @@
         <v>5</v>
       </c>
       <c r="P173">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q173">
         <v>239.63</v>
@@ -22630,7 +22630,7 @@
         <v>51</v>
       </c>
       <c r="P175">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q175">
         <v>1670.54</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="P176">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q176">
         <v>961.03</v>
@@ -22862,7 +22862,7 @@
         <v>7</v>
       </c>
       <c r="P177">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q177">
         <v>3081.3</v>
@@ -22978,7 +22978,7 @@
         <v>11</v>
       </c>
       <c r="P178">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q178">
         <v>613.95</v>
@@ -23094,7 +23094,7 @@
         <v>33</v>
       </c>
       <c r="P179">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q179">
         <v>345.22</v>
@@ -23210,7 +23210,7 @@
         <v>61</v>
       </c>
       <c r="P180">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q180">
         <v>175.65</v>
@@ -23326,7 +23326,7 @@
         <v>41</v>
       </c>
       <c r="P181">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q181">
         <v>2105.34</v>
@@ -23558,7 +23558,7 @@
         <v>6</v>
       </c>
       <c r="P183">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q183">
         <v>2326.94</v>
@@ -23674,7 +23674,7 @@
         <v>85</v>
       </c>
       <c r="P184">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q184">
         <v>4455.3</v>
@@ -23897,7 +23897,7 @@
         <v>2</v>
       </c>
       <c r="P186">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q186">
         <v>282.07</v>
@@ -24129,7 +24129,7 @@
         <v>25</v>
       </c>
       <c r="P188">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q188">
         <v>2834.16</v>
@@ -24361,7 +24361,7 @@
         <v>42</v>
       </c>
       <c r="P190">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q190">
         <v>10671.8</v>
@@ -24593,7 +24593,7 @@
         <v>67</v>
       </c>
       <c r="P192">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q192">
         <v>1351.04</v>
@@ -24825,7 +24825,7 @@
         <v>67</v>
       </c>
       <c r="P194">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q194">
         <v>438.53</v>
@@ -24941,7 +24941,7 @@
         <v>17</v>
       </c>
       <c r="P195">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q195">
         <v>259.83</v>
@@ -25057,7 +25057,7 @@
         <v>10</v>
       </c>
       <c r="P196">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q196">
         <v>98.84</v>
@@ -25173,7 +25173,7 @@
         <v>15</v>
       </c>
       <c r="P197">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q197">
         <v>1050.34</v>
@@ -25289,7 +25289,7 @@
         <v>8</v>
       </c>
       <c r="P198">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q198">
         <v>2357.1</v>
@@ -25405,7 +25405,7 @@
         <v>22</v>
       </c>
       <c r="P199">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q199">
         <v>160.91</v>
@@ -25521,7 +25521,7 @@
         <v>38</v>
       </c>
       <c r="P200">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q200">
         <v>20.73</v>
@@ -25637,7 +25637,7 @@
         <v>79</v>
       </c>
       <c r="P201">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q201">
         <v>1136.2</v>
